--- a/results/TNT_equivalence.xlsx
+++ b/results/TNT_equivalence.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670BD2B8-E716-4195-B7FD-657CA686BA9F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DE6E6C-0DF7-447B-85BB-BE8177C42B36}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{B157D900-312F-45CE-97D5-25C07FB39BFF}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{B157D900-312F-45CE-97D5-25C07FB39BFF}"/>
   </bookViews>
   <sheets>
     <sheet name="BAU" sheetId="2" r:id="rId1"/>
-    <sheet name="AON 84%" sheetId="4" r:id="rId2"/>
-    <sheet name="AON 100%" sheetId="5" r:id="rId3"/>
-    <sheet name="References" sheetId="1" r:id="rId4"/>
+    <sheet name="AON" sheetId="4" r:id="rId2"/>
+    <sheet name="References" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="45">
   <si>
     <t>Book:</t>
   </si>
@@ -368,55 +367,6 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>640080</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>3282032</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>159420</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B92F904-E4E5-474A-8EF8-1C332BC23D02}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="640080" y="2809875"/>
-          <a:ext cx="7499702" cy="3474120"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -963,7 +913,8 @@
         <v>14</v>
       </c>
       <c r="C4" s="1">
-        <v>77694.928600848798</v>
+        <f>37500*80/44/0.9</f>
+        <v>75757.575757575745</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
@@ -1015,7 +966,7 @@
       </c>
       <c r="C7" s="5">
         <f>C4*C2</f>
-        <v>31077.971440339519</v>
+        <v>30303.0303030303</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>15</v>
@@ -1050,7 +1001,7 @@
       </c>
       <c r="C9" s="5">
         <f>C8/(C7^(1/3))</f>
-        <v>3.1806492465293004</v>
+        <v>3.2075343299958265</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>31</v>
@@ -1068,7 +1019,7 @@
       </c>
       <c r="C10" s="5">
         <f>100*1616*(1+(C9/4.5)^2)/(((1+(C9/0.048)^2)^0.5)*((1+(C9/0.32)^2)^0.5)*((1+(C9/1.35)^2)^0.5))</f>
-        <v>143.0158028661163</v>
+        <v>140.4293847838324</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>34</v>
@@ -1086,7 +1037,7 @@
       </c>
       <c r="C11" s="8">
         <f>IF(-77.1+6.91*LN(C10*1000)&gt;0,-77.1+6.91*LN(C10*1000),0)</f>
-        <v>4.9266089516849689</v>
+        <v>4.8004988902697079</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="7" t="s">
@@ -1102,7 +1053,7 @@
       </c>
       <c r="C12" s="8">
         <f>IF(-15.6+1.93*LN(C10*100)&gt;0,-15.6+1.93*LN(C10*100),0)</f>
-        <v>2.8664818670123697</v>
+        <v>2.831258651595375</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="7" t="s">
@@ -1118,7 +1069,7 @@
       </c>
       <c r="C13" s="2">
         <f>290.69*C7^0.217</f>
-        <v>2743.4201227682438</v>
+        <v>2728.4284347357329</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>8</v>
@@ -1205,7 +1156,8 @@
         <v>14</v>
       </c>
       <c r="C4" s="1">
-        <v>36320.042282509799</v>
+        <f>37500*34/44/0.84</f>
+        <v>34496.753246753251</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
@@ -1258,7 +1210,7 @@
       </c>
       <c r="C7" s="5">
         <f>C2*C4*C5/C6</f>
-        <v>7109.7684135181908</v>
+        <v>6752.8535538298675</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>15</v>
@@ -1293,7 +1245,7 @@
       </c>
       <c r="C9" s="5">
         <f>C8/(C7^(1/3))</f>
-        <v>5.2005368945627222</v>
+        <v>5.2905914146849886</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>31</v>
@@ -1311,7 +1263,7 @@
       </c>
       <c r="C10" s="5">
         <f>100*1616*(1+(C9/4.5)^2)/(((1+(C9/0.048)^2)^0.5)*((1+(C9/0.32)^2)^0.5)*((1+(C9/1.35)^2)^0.5))</f>
-        <v>53.754825141332923</v>
+        <v>52.135164348340382</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>34</v>
@@ -1345,7 +1297,7 @@
       </c>
       <c r="C12" s="8">
         <f>IF(-15.6+1.93*LN(C10*100)&gt;0,-15.6+1.93*LN(C10*100),0)</f>
-        <v>0.97793498474349683</v>
+        <v>0.91888900391034589</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="7" t="s">
@@ -1361,7 +1313,7 @@
       </c>
       <c r="C13" s="2">
         <f>290.69*C7^0.217</f>
-        <v>1991.9696886141626</v>
+        <v>1969.8304330497881</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>8</v>
@@ -1378,249 +1330,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E9B78F-0451-4F8A-8BA2-AE154C8B7ECC}">
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="1">
-        <v>17.030999999999999</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1">
-        <v>30690.502543064998</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="5">
-        <f>18.346*1000</f>
-        <v>18346</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="5">
-        <v>4686</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="5">
-        <f>C2*C4*C5/C6</f>
-        <v>6007.7673885517552</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="4">
-        <v>100</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="5">
-        <f>C8/(C7^(1/3))</f>
-        <v>5.5008393741389199</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="5">
-        <f>100*1616*(1+(C9/4.5)^2)/(((1+(C9/0.048)^2)^0.5)*((1+(C9/0.32)^2)^0.5)*((1+(C9/1.35)^2)^0.5))</f>
-        <v>48.682751047412303</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="8">
-        <f>IF(-77.1+6.91*LN(C10*1000)&gt;0,-77.1+6.91*LN(C10*1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="8">
-        <f>IF(-15.6+1.93*LN(C10*100)&gt;0,-15.6+1.93*LN(C10*100),0)</f>
-        <v>0.78665528322031797</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="2">
-        <f>290.69*C7^0.217</f>
-        <v>1920.484633561894</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EE899A6-458A-4CC8-A0E7-751D131F0334}">
   <dimension ref="B2:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/results/TNT_equivalence.xlsx
+++ b/results/TNT_equivalence.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DE6E6C-0DF7-447B-85BB-BE8177C42B36}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068A5054-90D3-46C4-B238-BCE3CAEDBBAC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{B157D900-312F-45CE-97D5-25C07FB39BFF}"/>
   </bookViews>
@@ -224,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -249,6 +249,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -913,8 +916,7 @@
         <v>14</v>
       </c>
       <c r="C4" s="1">
-        <f>37500*80/44/0.9</f>
-        <v>75757.575757575745</v>
+        <v>76816.994254790305</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
@@ -966,7 +968,7 @@
       </c>
       <c r="C7" s="5">
         <f>C4*C2</f>
-        <v>30303.0303030303</v>
+        <v>30726.797701916123</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>15</v>
@@ -1001,7 +1003,7 @@
       </c>
       <c r="C9" s="5">
         <f>C8/(C7^(1/3))</f>
-        <v>3.2075343299958265</v>
+        <v>3.1927204912928278</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>31</v>
@@ -1019,7 +1021,7 @@
       </c>
       <c r="C10" s="5">
         <f>100*1616*(1+(C9/4.5)^2)/(((1+(C9/0.048)^2)^0.5)*((1+(C9/0.32)^2)^0.5)*((1+(C9/1.35)^2)^0.5))</f>
-        <v>140.4293847838324</v>
+        <v>141.84521618497229</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>34</v>
@@ -1037,7 +1039,7 @@
       </c>
       <c r="C11" s="8">
         <f>IF(-77.1+6.91*LN(C10*1000)&gt;0,-77.1+6.91*LN(C10*1000),0)</f>
-        <v>4.8004988902697079</v>
+        <v>4.8698177520711141</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="7" t="s">
@@ -1053,7 +1055,7 @@
       </c>
       <c r="C12" s="8">
         <f>IF(-15.6+1.93*LN(C10*100)&gt;0,-15.6+1.93*LN(C10*100),0)</f>
-        <v>2.831258651595375</v>
+        <v>2.8506197808684153</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="7" t="s">
@@ -1067,9 +1069,9 @@
       <c r="B13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="10">
         <f>290.69*C7^0.217</f>
-        <v>2728.4284347357329</v>
+        <v>2736.6631621341753</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>8</v>
@@ -1156,8 +1158,7 @@
         <v>14</v>
       </c>
       <c r="C4" s="1">
-        <f>37500*34/44/0.84</f>
-        <v>34496.753246753251</v>
+        <v>30690.5025481741</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
@@ -1210,7 +1211,7 @@
       </c>
       <c r="C7" s="5">
         <f>C2*C4*C5/C6</f>
-        <v>6752.8535538298675</v>
+        <v>6007.7673895518783</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>15</v>
@@ -1245,7 +1246,7 @@
       </c>
       <c r="C9" s="5">
         <f>C8/(C7^(1/3))</f>
-        <v>5.2905914146849886</v>
+        <v>5.500839373833676</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>31</v>
@@ -1263,7 +1264,7 @@
       </c>
       <c r="C10" s="5">
         <f>100*1616*(1+(C9/4.5)^2)/(((1+(C9/0.048)^2)^0.5)*((1+(C9/0.32)^2)^0.5)*((1+(C9/1.35)^2)^0.5))</f>
-        <v>52.135164348340382</v>
+        <v>48.682751052117055</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>34</v>
@@ -1297,7 +1298,7 @@
       </c>
       <c r="C12" s="8">
         <f>IF(-15.6+1.93*LN(C10*100)&gt;0,-15.6+1.93*LN(C10*100),0)</f>
-        <v>0.91888900391034589</v>
+        <v>0.78665528340683188</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="7" t="s">
@@ -1311,9 +1312,9 @@
       <c r="B13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="10">
         <f>290.69*C7^0.217</f>
-        <v>1969.8304330497881</v>
+        <v>1920.4846336312701</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>8</v>

--- a/results/TNT_equivalence.xlsx
+++ b/results/TNT_equivalence.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068A5054-90D3-46C4-B238-BCE3CAEDBBAC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002C861E-8EA2-4348-BAEC-4629DAFB6488}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{B157D900-312F-45CE-97D5-25C07FB39BFF}"/>
   </bookViews>
@@ -966,7 +966,7 @@
       <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="8">
         <f>C4*C2</f>
         <v>30726.797701916123</v>
       </c>
@@ -1019,7 +1019,7 @@
       <c r="B10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="8">
         <f>100*1616*(1+(C9/4.5)^2)/(((1+(C9/0.048)^2)^0.5)*((1+(C9/0.32)^2)^0.5)*((1+(C9/1.35)^2)^0.5))</f>
         <v>141.84521618497229</v>
       </c>
@@ -1209,7 +1209,7 @@
       <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="8">
         <f>C2*C4*C5/C6</f>
         <v>6007.7673895518783</v>
       </c>
@@ -1262,7 +1262,7 @@
       <c r="B10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="8">
         <f>100*1616*(1+(C9/4.5)^2)/(((1+(C9/0.048)^2)^0.5)*((1+(C9/0.32)^2)^0.5)*((1+(C9/1.35)^2)^0.5))</f>
         <v>48.682751052117055</v>
       </c>

--- a/results/TNT_equivalence.xlsx
+++ b/results/TNT_equivalence.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002C861E-8EA2-4348-BAEC-4629DAFB6488}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE070A05-D1EF-46B1-BB01-705AF4A6F1AF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{B157D900-312F-45CE-97D5-25C07FB39BFF}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="9060" activeTab="2" xr2:uid="{B157D900-312F-45CE-97D5-25C07FB39BFF}"/>
   </bookViews>
   <sheets>
     <sheet name="BAU" sheetId="2" r:id="rId1"/>
     <sheet name="AON" sheetId="4" r:id="rId2"/>
-    <sheet name="References" sheetId="1" r:id="rId3"/>
+    <sheet name="AO" sheetId="5" r:id="rId3"/>
+    <sheet name="References" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="47">
   <si>
     <t>Book:</t>
   </si>
@@ -175,6 +176,12 @@
   </si>
   <si>
     <t>Maximum distance at which projectiles can land</t>
+  </si>
+  <si>
+    <t>Molar mass of hydrogen</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0360319920330627</t>
   </si>
 </sst>
 </file>
@@ -370,6 +377,55 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>640080</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3278857</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>159420</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BD26102-008C-4CF2-859D-ED2DF28353B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="640080" y="2809875"/>
+          <a:ext cx="7496527" cy="3474120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1331,6 +1387,246 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF514AE-34DD-4A6E-AD9A-65383C43186D}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0156800000000001</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2469.3749935075198</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="5">
+        <v>4008.82</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5">
+        <v>4686</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="8">
+        <f>28.65*C4</f>
+        <v>70747.593563990435</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="4">
+        <v>100</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="5">
+        <f>C8/(C7^(1/3))</f>
+        <v>2.4178504913719143</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="8">
+        <f>100*1616*(1+(C9/4.5)^2)/(((1+(C9/0.048)^2)^0.5)*((1+(C9/0.32)^2)^0.5)*((1+(C9/1.35)^2)^0.5))</f>
+        <v>264.38992909835622</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="8">
+        <f>IF(-77.1+6.91*LN(C10*1000)&gt;0,-77.1+6.91*LN(C10*1000),0)</f>
+        <v>9.1725958494445621</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="8">
+        <f>IF(-15.6+1.93*LN(C10*100)&gt;0,-15.6+1.93*LN(C10*100),0)</f>
+        <v>4.0524087429423314</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="10">
+        <f>290.69*C7^0.217</f>
+        <v>3279.5746799282788</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EE899A6-458A-4CC8-A0E7-751D131F0334}">
   <dimension ref="B2:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
